--- a/www/download/COUNTRY.IND.rpO1.xlsx
+++ b/www/download/COUNTRY.IND.rpO1.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>Índia</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Ochoa 1</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,2523 +852,4084 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>32.3624597460212</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.082</t>
+          <t>35.4233080157224</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.083</t>
+          <t>36.2844710313904</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>41.203131834449</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.086</t>
+          <t>43.0477838422277</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.091</t>
+          <t>44.9034582986076</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.098</t>
+          <t>47.1920697216164</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.103</t>
+          <t>48.6144866907991</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>46.554935412596</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>45.3103761812977</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.166</t>
+          <t>44.0917118830387</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.191</t>
+          <t>45.2898541499635</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.247</t>
+          <t>41.2711521319086</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.268</t>
+          <t>43.2393174685843</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.277</t>
+          <t>48.3687622444747</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>380.787</t>
+          <t>2.09497597679835</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>393.501</t>
+          <t>2.03254429287375</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>397.971</t>
+          <t>1.98571969254371</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>401.547</t>
+          <t>2.00680246205989</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>398.413</t>
+          <t>2.14778359601595</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>416.883</t>
+          <t>2.01596978653251</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>432.376</t>
+          <t>1.87968598430778</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>424.206</t>
+          <t>1.87733570944902</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>449.023</t>
+          <t>1.91950375467603</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>457.9</t>
+          <t>1.79474494207034</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>469.777</t>
+          <t>1.82312781930401</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>471.768</t>
+          <t>1.76498214335131</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>460.23</t>
+          <t>1.7012999715635</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>463.379</t>
+          <t>1.63308653895073</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>465.828</t>
+          <t>1.57875536457891</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>176.495</t>
+          <t>3.27119192090781</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>182.775</t>
+          <t>3.1544056891709</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>185.732</t>
+          <t>3.06705354169366</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>188.117</t>
+          <t>3.0778747663194</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>187.86</t>
+          <t>3.22726916248107</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>194.375</t>
+          <t>3.20352345824335</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>198.162</t>
+          <t>3.15467994538164</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>192.288</t>
+          <t>3.27963772849095</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>198.163</t>
+          <t>3.47065715777906</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>198.994</t>
+          <t>3.39663899571536</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>199.767</t>
+          <t>3.42065206251291</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>197.538</t>
+          <t>3.32681187168767</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>191.106</t>
+          <t>3.22102173438172</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>193.616</t>
+          <t>3.11666794229365</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>195.621</t>
+          <t>3.03070206141613</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>883269.411</t>
+          <t>4.49254863651911</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>912034.175</t>
+          <t>4.30508769914675</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>921899.495</t>
+          <t>4.16119011591032</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>929558.011</t>
+          <t>4.14779765764281</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>921995.643</t>
+          <t>4.3018657952424</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>963502.007</t>
+          <t>4.29531930393404</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1001482.189</t>
+          <t>4.20568254656947</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>985730.519</t>
+          <t>4.34325065162572</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>1045978.848</t>
+          <t>4.54987984769947</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>1068687.044</t>
+          <t>4.4238077722342</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>1098153.176</t>
+          <t>4.42113303644234</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>1102781.829</t>
+          <t>4.31115689985104</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>1077429.619</t>
+          <t>4.1829701208543</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>1085691.063</t>
+          <t>4.05700644786553</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>1092178.443</t>
+          <t>3.94951705929536</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>408729.533</t>
+          <t>21060393820932</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>422740.685</t>
+          <t>18461154757292.1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>429173.719</t>
+          <t>21577848998470.2</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>434229.587</t>
+          <t>23158879071099.5</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>433336.133</t>
+          <t>25758638208581.9</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>447690.05</t>
+          <t>31344476702479.4</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>457931.785</t>
+          <t>34480908635137.6</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>446355.698</t>
+          <t>34324299597503.5</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>461695.026</t>
+          <t>37838084853173</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>465360.993</t>
+          <t>36902290952068.2</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>468780.92</t>
+          <t>38636461287942.2</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>463833.094</t>
+          <t>38460722599823.1</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>449591.928</t>
+          <t>36211130121369.6</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>455869.88</t>
+          <t>29334324510395.1</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>460912.884</t>
+          <t>28946235118618.6</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>21.54</t>
+          <t>2217920798613.55</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>21.53</t>
+          <t>1932505852837.46</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>21.51</t>
+          <t>2302655042131.73</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>21.49</t>
+          <t>2563985105494.44</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>21.47</t>
+          <t>2853237404051.37</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>23.53</t>
+          <t>3283772219469.61</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>25.59</t>
+          <t>3605110879134.26</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>27.65</t>
+          <t>3585134954154.33</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>29.7</t>
+          <t>3937226489498.61</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>31.76</t>
+          <t>3751576878741.74</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>31.76</t>
+          <t>3887638675128.61</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>31.76</t>
+          <t>3702883534064.88</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>31.76</t>
+          <t>3428684874245.13</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>31.76</t>
+          <t>2799543910122.75</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>31.76</t>
+          <t>2852949836461.57</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>42.66</t>
+          <t>796242967.733712</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>676271107.133819</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>44.34</t>
+          <t>728826958.618166</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>45.18</t>
+          <t>806725623.233051</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>46.02</t>
+          <t>873805326.614818</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>44.45</t>
+          <t>1036842596.95928</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>42.87</t>
+          <t>1118570543.96736</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>1038803354.75322</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>39.73</t>
+          <t>973527213.904382</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>38.16</t>
+          <t>788608554.012113</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>38.16</t>
+          <t>713052137.292196</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>38.16</t>
+          <t>620936695.262146</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>38.16</t>
+          <t>464237431.418217</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>38.16</t>
+          <t>351366438.695082</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>38.16</t>
+          <t>342816286.070996</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>35.8</t>
+          <t>464751.220122989</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>34.98</t>
+          <t>462225.190128577</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>34.15</t>
+          <t>528178.564942368</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>33.33</t>
+          <t>517150.458182678</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>32.51</t>
+          <t>538216.626538421</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>32.02</t>
+          <t>565535.869615884</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>31.54</t>
+          <t>595670.984467333</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>31.05</t>
+          <t>615476.494244154</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>30.57</t>
+          <t>708946.566709688</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>30.08</t>
+          <t>824144.0978425</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>30.08</t>
+          <t>964999.467285376</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>30.08</t>
+          <t>1076508.02564932</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>30.08</t>
+          <t>1351701.33373941</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>30.08</t>
+          <t>1461643.56906982</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>30.08</t>
+          <t>1556367.84706584</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>13.64</t>
+          <t>946805.438671238</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>13.82</t>
+          <t>932209.578156858</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>13.99</t>
+          <t>1066700.01934219</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>14.17</t>
+          <t>1038969.68504953</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>14.35</t>
+          <t>1077187.67469671</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>15.31</t>
+          <t>1155756.15957009</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>16.27</t>
+          <t>1202225.18650366</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>17.23</t>
+          <t>1251249.5167042</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>18.18</t>
+          <t>1449298.58403458</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>19.14</t>
+          <t>1698854.27522354</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>19.14</t>
+          <t>1991032.09807453</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>19.14</t>
+          <t>2299044.1599376</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>19.14</t>
+          <t>2886634.87460927</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>19.14</t>
+          <t>3115535.31729514</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>19.14</t>
+          <t>3200711.10547914</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>39.31</t>
+          <t>3.48247763902001</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>40.03</t>
+          <t>3.34948286612086</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>40.76</t>
+          <t>3.23727840014695</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>41.48</t>
+          <t>3.21446822118743</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>42.21</t>
+          <t>3.34712982951139</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>41.57</t>
+          <t>3.26195613203209</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>40.94</t>
+          <t>3.14723922677356</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>40.3</t>
+          <t>3.20613194979985</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>39.67</t>
+          <t>3.32404990467478</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>39.04</t>
+          <t>3.19872071751742</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>39.04</t>
+          <t>3.22717304870097</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>39.04</t>
+          <t>3.14256064947788</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>39.04</t>
+          <t>3.05049920433421</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>39.04</t>
+          <t>2.94975498607655</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>39.04</t>
+          <t>2.8666314822584</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>47.05</t>
+          <t>79659.7714734204</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>46.15</t>
+          <t>81953.3621818118</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>45.25</t>
+          <t>83116.05102857</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>44.35</t>
+          <t>79258.8713993947</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>43.44</t>
+          <t>86424.6759602973</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>43.12</t>
+          <t>91264.8480153773</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>42.79</t>
+          <t>97869.6705282442</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>42.47</t>
+          <t>102907.829816439</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>42.15</t>
+          <t>120416.277661068</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>41.82</t>
+          <t>138799.355526106</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>41.82</t>
+          <t>166184.524876129</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>41.82</t>
+          <t>191436.933187129</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>41.82</t>
+          <t>247279.834367286</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>41.82</t>
+          <t>268488.565290632</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>41.82</t>
+          <t>276598.975512559</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>32.3624597460212</t>
+          <t>12566.4964566776</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>35.4233080157224</t>
+          <t>10573.1682795049</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>36.2844710313904</t>
+          <t>12397.7341610449</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>41.203131834449</t>
+          <t>13629.7234993135</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>43.0477838422277</t>
+          <t>15188.0821205627</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>44.9034582986076</t>
+          <t>16893.9933589363</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>47.1920697216164</t>
+          <t>18192.7705584636</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>48.6144866907991</t>
+          <t>18644.5740272557</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>46.554935412596</t>
+          <t>19868.6167205908</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>45.3103761812977</t>
+          <t>18852.7120785615</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>44.0917118830387</t>
+          <t>19460.887288689</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>45.2898541499635</t>
+          <t>18745.1430713813</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>41.2711521319086</t>
+          <t>17941.3143804498</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>43.2393174685843</t>
+          <t>14459.2814249424</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>48.3687622444747</t>
+          <t>14584.0664267495</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.124</t>
+          <t>-8735885784.45262</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>121507766555.642</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>56958442654.424</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>122866825761.814</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.146</t>
+          <t>168769213243.091</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.148</t>
+          <t>202304943253.053</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.153</t>
+          <t>303664536495.474</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.158</t>
+          <t>642737515111.787</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.182</t>
+          <t>968868750492.587</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>1146315233375.7</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.245</t>
+          <t>1260799412726.34</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.273</t>
+          <t>1425433262733.16</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.337</t>
+          <t>1269561940433.52</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.368</t>
+          <t>978811401172.394</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.387</t>
+          <t>613316564388.788</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.198</t>
+          <t>47533156812.3553</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.196</t>
+          <t>119940449914.41</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.221</t>
+          <t>53334325609.492</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.219</t>
+          <t>112744356204.363</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.229</t>
+          <t>93797135054.6702</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.237</t>
+          <t>14138202147.2698</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.247</t>
+          <t>16580964934.7436</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.257</t>
+          <t>182137670965.326</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>256793396952.035</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.348</t>
+          <t>291418001058.458</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.405</t>
+          <t>325098594404.383</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.454</t>
+          <t>531020704345.611</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.567</t>
+          <t>487588057305.301</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.618</t>
+          <t>360676763881.931</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.644</t>
+          <t>194068616853.36</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.843</t>
+          <t>-56269042596.808</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.877</t>
+          <t>1567316641.23164</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0.942</t>
+          <t>3624117044.932</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0.917</t>
+          <t>10122469557.4514</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.958</t>
+          <t>74972078188.4206</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>1.022</t>
+          <t>188166741105.783</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>287083571560.731</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1.159</t>
+          <t>460599844146.461</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>1.337</t>
+          <t>712075353540.552</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>854897232317.239</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>1.842</t>
+          <t>935700818321.955</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2.076</t>
+          <t>894412558387.549</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>2.659</t>
+          <t>781973883128.219</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>2.948</t>
+          <t>618134637290.463</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2.99</t>
+          <t>419247947535.428</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.727</t>
+          <t>56329.0393678813</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.754</t>
+          <t>45987.814272319</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.829</t>
+          <t>52532.6511713595</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.827</t>
+          <t>57442.0365514281</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.866</t>
+          <t>66024.5648393669</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.902</t>
+          <t>72001.4585906279</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.925</t>
+          <t>75449.7717037515</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.983</t>
+          <t>78421.5385064489</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>1.159</t>
+          <t>85912.8902366905</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>1.372</t>
+          <t>79157.2727856472</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>1.611</t>
+          <t>82264.5382505535</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>1.853</t>
+          <t>77652.8920563369</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>2.341</t>
+          <t>72671.2796227218</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2.544</t>
+          <t>57110.6189032504</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>2.591</t>
+          <t>56391.2103850175</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>42384.7659837909</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.372</t>
+          <t>36797.5370985156</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.404</t>
+          <t>43169.2184060072</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.409</t>
+          <t>47789.246222449</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.435</t>
+          <t>54650.8378324307</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.448</t>
+          <t>62565.7074653199</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.464</t>
+          <t>67680.781763452</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.486</t>
+          <t>69209.1879153958</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>72856.7503433433</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.664</t>
+          <t>69670.6795366619</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.781</t>
+          <t>70855.6492375992</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.882</t>
+          <t>68298.7969388156</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>1.114</t>
+          <t>65833.0883091072</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>1.225</t>
+          <t>53419.8664210896</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>1.258</t>
+          <t>54239.5513270695</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>209.5</t>
+          <t>42190.4443609062</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>203.25</t>
+          <t>44308.7304213983</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>198.57</t>
+          <t>47568.3231940199</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>200.68</t>
+          <t>49617.2512347252</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>214.78</t>
+          <t>55007.2540389052</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>201.6</t>
+          <t>67708.288287402</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>187.97</t>
+          <t>66875.4175146345</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>187.73</t>
+          <t>77841.1161473401</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>191.95</t>
+          <t>88181.7103564999</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>179.47</t>
+          <t>123820.217757189</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>182.31</t>
+          <t>157727.971292324</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>176.5</t>
+          <t>198123.928664349</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>170.13</t>
+          <t>242725.113223604</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>163.31</t>
+          <t>259622.878233011</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>157.88</t>
+          <t>227253.968468943</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>327.12</t>
+          <t>1318583354212.82</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>315.44</t>
+          <t>1167349688398.02</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>306.71</t>
+          <t>1360607671933.77</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>307.79</t>
+          <t>1519618665023.08</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>322.73</t>
+          <t>1866730187739.76</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>320.35</t>
+          <t>2657075259996.48</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>315.47</t>
+          <t>2759863827445.45</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>327.96</t>
+          <t>2822587866224.69</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>347.07</t>
+          <t>2743793270275.75</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>339.66</t>
+          <t>3018376780999.1</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>342.07</t>
+          <t>3386169148931.4</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>332.68</t>
+          <t>3594522882127.95</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>322.1</t>
+          <t>3282098801939.24</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>311.67</t>
+          <t>2706271177377.77</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>303.07</t>
+          <t>2331718659679.07</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>449.25</t>
+          <t>43742.1386943222</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>430.51</t>
+          <t>45931.4174722332</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>416.12</t>
+          <t>49032.7622933105</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>414.78</t>
+          <t>52971.8074865367</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>430.19</t>
+          <t>59759.2850203407</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>429.53</t>
+          <t>66742.1545757755</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>420.57</t>
+          <t>65686.0833914531</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>434.33</t>
+          <t>74883.5861957074</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>454.99</t>
+          <t>86656.9215268048</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>442.38</t>
+          <t>128122.543510154</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>442.11</t>
+          <t>169922.116329699</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>431.12</t>
+          <t>213375.178266109</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>418.3</t>
+          <t>268350.444200915</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>405.7</t>
+          <t>294846.686007943</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>394.95</t>
+          <t>267974.340420028</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>16139586.085</t>
+          <t>1366479569640.15</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>14479861.687</t>
+          <t>1341667471553.33</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>17180086.511</t>
+          <t>1466384127255.65</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>19189622.513</t>
+          <t>1768285729030.92</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>21773594.799</t>
+          <t>2227373088481.77</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>26082596.044</t>
+          <t>2815417794634.78</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>29263528.85</t>
+          <t>3005331249897.82</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>29358938.424</t>
+          <t>3325803218313.64</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>32714374.878</t>
+          <t>3644905633635.58</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>31902177.964</t>
+          <t>4321509667822.35</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>33286370.706</t>
+          <t>5042105331293.16</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>32221183.939</t>
+          <t>5441287333934.99</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>30298367.565</t>
+          <t>5072895247559.76</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>24753626.604</t>
+          <t>4214657702445.32</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>25266284.091</t>
+          <t>3547445008585.87</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>9941780.385</t>
+          <t>-1551.69433341598</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>8405401.096</t>
+          <t>-1622.68705083492</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>9756990.473</t>
+          <t>-1464.43909929061</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>10805833.747</t>
+          <t>-3354.55625181147</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>12403393.43</t>
+          <t>-4752.03098143559</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>13995293.147</t>
+          <t>966.133711626524</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>14951257.255</t>
+          <t>1189.33412318138</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>15079550.675</t>
+          <t>2957.52995163274</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>17024763.827</t>
+          <t>1524.78882969508</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>15751823.564</t>
+          <t>-4302.32575296547</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>16433721.431</t>
+          <t>-12194.145037375</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>15339419.618</t>
+          <t>-15251.2496017601</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>13887885.355</t>
+          <t>-25625.3309773102</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>11057512.518</t>
+          <t>-35223.8077749327</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>11031305.655</t>
+          <t>-40720.3719510847</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>21060393.821</t>
+          <t>-47896215427.3322</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>18461154.757</t>
+          <t>-174317783155.311</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>21577848.998</t>
+          <t>-105776455321.876</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>23158879.071</t>
+          <t>-248667064007.842</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>25758638.209</t>
+          <t>-360642900742.012</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>31344476.702</t>
+          <t>-158342534638.297</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>34480908.635</t>
+          <t>-245467422452.369</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>34324299.598</t>
+          <t>-503215352088.95</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>37838084.853</t>
+          <t>-901112363359.833</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>36902290.952</t>
+          <t>-1303132886823.25</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>38636461.288</t>
+          <t>-1655936182361.76</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>38460722.6</t>
+          <t>-1846764451807.04</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>36211130.121</t>
+          <t>-1790796445620.52</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>29334324.51</t>
+          <t>-1508386525067.54</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>28946235.119</t>
+          <t>-1215726348906.8</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.947</t>
+          <t>223060.94208</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.932</t>
+          <t>238101.96924</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.067</t>
+          <t>254778.66558</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>1.039</t>
+          <t>256143.10173</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>1.077</t>
+          <t>266821.27946</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>1.156</t>
+          <t>271913.7645</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1.202</t>
+          <t>275570.49268</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>1.251</t>
+          <t>284632.24895</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>1.449</t>
+          <t>334641.38392</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>1.699</t>
+          <t>391168.90014</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>1.991</t>
+          <t>461093.23389</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>2.299</t>
+          <t>519295.997</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>2.887</t>
+          <t>653130.30221</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>3.116</t>
+          <t>701350.80033</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>3.201</t>
+          <t>712642.83225</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>10337756.127</t>
+          <t>0.0853601014596236</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>9153747.148</t>
+          <t>0.106629137080085</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>10684313.408</t>
+          <t>0.105335874398919</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>11527405.559</t>
+          <t>0.120755109345244</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>12870298.915</t>
+          <t>0.125374515917872</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>15337513.664</t>
+          <t>0.117513751566945</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>17084384.043</t>
+          <t>0.10902738797338</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>16883762.432</t>
+          <t>0.108536406939624</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>18509077.869</t>
+          <t>0.112044799891841</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>17901950.584</t>
+          <t>0.112192952735706</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>18726048.966</t>
+          <t>0.114306947854305</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>18008908.777</t>
+          <t>0.113735137375341</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>16956295.135</t>
+          <t>0.112666402508448</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>13762105.836</t>
+          <t>0.114776018866656</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>14075306.439</t>
+          <t>0.116294885052</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.465</t>
+          <t>123613.527569007</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.462</t>
+          <t>120048.866053424</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.528</t>
+          <t>139339.845934098</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.517</t>
+          <t>139753.09091733</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.538</t>
+          <t>146077.221231</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.566</t>
+          <t>148492.076719936</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.596</t>
+          <t>152614.816485931</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.615</t>
+          <t>157697.743396309</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.709</t>
+          <t>182469.015584059</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.824</t>
+          <t>210392.821080105</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.965</t>
+          <t>245138.93048999</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>1.077</t>
+          <t>272797.882795781</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>1.352</t>
+          <t>337414.481954298</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>1.462</t>
+          <t>368490.321395703</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>1.556</t>
+          <t>386510.154509205</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2217920.799</t>
+          <t>198089.070790303</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>1932505.853</t>
+          <t>196162.657726759</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2302655.042</t>
+          <t>221371.657877838</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2563985.105</t>
+          <t>219220.329306488</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2853237.404</t>
+          <t>228724.289692498</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>3283772.219</t>
+          <t>236706.271197512</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>3605110.879</t>
+          <t>247082.297465197</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>3585134.954</t>
+          <t>257128.621463448</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>3937226.489</t>
+          <t>299841.647733577</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>3751576.879</t>
+          <t>347623.532582441</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>3887638.675</t>
+          <t>404651.235885026</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>3702883.534</t>
+          <t>454079.252238379</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>3428684.874</t>
+          <t>567246.968696692</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>2799543.91</t>
+          <t>617745.031017299</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>2852949.836</t>
+          <t>643862.68391602</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>348.25</t>
+          <t>843277.635398844</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>334.95</t>
+          <t>876969.433422282</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>323.73</t>
+          <t>942357.87911787</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>321.45</t>
+          <t>916608.381659981</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>334.71</t>
+          <t>958236.780478598</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>326.2</t>
+          <t>1022074.4888626</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>314.72</t>
+          <t>1089764.88600799</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>320.61</t>
+          <t>1159366.17728751</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>332.4</t>
+          <t>1337197.4616402</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>319.87</t>
+          <t>1579909.15284148</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>322.72</t>
+          <t>1842048.50694835</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>314.26</t>
+          <t>2075769.18525513</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>305.05</t>
+          <t>2658636.57804784</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>294.98</t>
+          <t>2948367.05553636</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>286.66</t>
+          <t>2990188.09248265</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>796.243</t>
+          <t>198089.070790303</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>676.271</t>
+          <t>198694.967531973</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>728.827</t>
+          <t>214749.468349746</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>806.726</t>
+          <t>222901.514059908</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>873.805</t>
+          <t>234115.619268022</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>1036.843</t>
+          <t>246559.834273214</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1118.571</t>
+          <t>263107.175047203</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>1038.803</t>
+          <t>273303.033492786</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>973.527</t>
+          <t>293967.325335853</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>788.609</t>
+          <t>314411.843292728</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>713.052</t>
+          <t>342574.500922912</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>620.937</t>
+          <t>377898.744723867</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>464.237</t>
+          <t>410522.763912039</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>351.366</t>
+          <t>438591.361179476</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>342.816</t>
+          <t>482183.000180849</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>123613.527569007</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>121832.953115175</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>135504.481687451</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>141712.786034959</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>148679.592805464</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>153851.37034201</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>160976.186305388</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>166410.482191631</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>177484.835356938</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>188824.925215769</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>207129.94008064</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>228277.309557297</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>246120.937408318</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>263931.76050548</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>293786.840308781</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>151642.035989697</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>175463.856113241</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>182380.142222162</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>189944.016753512</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>206563.148447502</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>211372.655582488</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>216683.889554803</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>228741.269026552</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>270242.299666423</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>316054.028437559</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>376743.467504974</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>427524.826631621</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>546818.853193308</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>606890.398082701</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>624342.556011689</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>9941780384902.62</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>8405401095594.81</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>9756990473014.23</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>10805833746704.2</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>12403393429829.4</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>13995293146965.1</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>14951257254813.7</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>15079550675012.8</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>17024763826599.5</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>15751823564132.3</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>16433721430591.2</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>15339419617816.8</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>13887885355042.6</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>11057512517747.6</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>11031305654966.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>16139586085320.5</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>14479861687263.6</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>17180086511284.1</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>19189622513459.5</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>21773594798737.2</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>26082596043994.6</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>29263528849724.3</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>29358938424040.5</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>32714374878065.4</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>31902177963662</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>33286370706307.7</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>32221183938755</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>30298367564980.5</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>24753626604233.8</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>25266284090694.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>10337756126839.7</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>9153747148311.97</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>10684313407609.5</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>11527405558560.9</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>12870298914950.1</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>15337513663942.1</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>17084384042687.9</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>16883762432374.8</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>18509077869137.6</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>17901950584320.7</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>18726048965615.7</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>18008908777161.4</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>16956295135141.4</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>13762105836389.9</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>14075306438967.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>380787429.414916</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>393500838.072331</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>397970756.609609</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>401546875.716261</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>398412827</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>416883259.227144</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>432375751.095812</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>424205792.732751</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>449023250.747477</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>457899624</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>469777231.09542</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>471767957.605752</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>460230081</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>463378669.072472</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>465827675.054621</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>176494761.786607</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>182774529.04854</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>185731925.86811</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>188117176.817533</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>187860282.911458</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>194375133.794676</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>198161729.547954</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>192288381.001002</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>198163090.308057</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>198994015.455626</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>199766774.117651</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>197538291.383765</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>191105556.791384</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>193615701.074433</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>195621012.204717</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>883269411041.813</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>912034175416.31</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>921899495067.775</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>929558010777.49</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>921995642624.479</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>963502007286.061</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1001482188929.38</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>985730519159.591</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>1045978847742.94</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>1068687043754.34</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>1098153176017.84</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>1102781829254.43</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>1077429618585.69</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>1085691063414.01</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>1092178442629.47</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>408729532907.89</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>422740684945.954</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>429173719058.416</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>434229587334.143</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>433336132594.373</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>447690050382.461</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>457931785421.459</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>446355698248.271</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>461695025670.482</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>465360993412.491</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>468780919950.533</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>463833093857.914</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>449591927559.544</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>455869880085.226</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>460912884317.789</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0.215449898684455</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>0.215273192986451</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0.215096487288446</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>0.214919781590441</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>0.214743075892436</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>0.235313607787725</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0.255884139683014</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0.276454671578303</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0.297025203473592</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0.317595735368881</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>0.317595735368881</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>0.317595735368881</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0.317595735368881</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>0.317595735368881</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>0.317595735368881</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>0.426572864616802</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>0.434971395509284</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0.443369926401766</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>0.451768457294249</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>0.460166988186731</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>0.444450156426241</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0.428733324665752</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0.413016492905263</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0.397299661144773</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0.381582829384284</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>0.381582829384284</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0.381582829384284</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0.381582829384284</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>0.381582829384284</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>0.381582829384284</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0.357977236698742</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>0.349755411504265</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0.341533586309788</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>0.333311761115311</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>0.325089935920834</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>0.320236235786034</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0.315382535651234</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0.310528835516434</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0.305675135381635</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0.300821435246835</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>0.300821435246835</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0.300821435246835</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0.300821435246835</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>0.300821435246835</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>0.300821435246835</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>0.136395434894175</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>0.138168353847534</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0.139941272800893</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>0.141714191754252</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>0.143487110707611</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>0.153075098503735</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>0.162663086299858</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0.172251074095982</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0.181839061892105</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0.191427049688229</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>0.191427049688229</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0.191427049688229</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0.191427049688229</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>0.191427049688229</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>0.191427049688229</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>0.393099495319025</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>0.400344820934381</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0.407590146549737</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>0.414835472165093</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>0.422080797780449</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>0.415736576939963</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0.409392356099476</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0.40304813525899</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0.396703914418503</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>0.390359693578017</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>0.390359693578017</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>0.390359693578017</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>0.390359693578017</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>0.390359693578017</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>0.390359693578017</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>0.4705050697868</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>0.461486825218085</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0.45246858064937</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>0.443450336080655</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>0.43443209151194</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>0.431188324556303</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>0.427944557600666</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0.424700790645029</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0.421457023689391</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>0.418213256733754</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>0.418213256733754</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>0.418213256733754</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>0.418213256733754</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>0.418213256733754</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>0.418213256733754</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>727386.69902</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>754103.19355</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>829047.77571</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>827157.17116</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>866029.74744</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>902411.61575</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>925415.9909</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>982647.65615</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>1159060.31364</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>1371614.28394</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>1610529.88414</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>1853051.59181</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>2340827.68566</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>2543922.83553</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>2590618.46841</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>349731.10678</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>371626.51384</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>403751.8001</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>409164.34606</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>435287.43814</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>448078.92678</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>463766.18702</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>485869.89049</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>570083.9474</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>663677.56102</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>781394.70339</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>881604.07887</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>1114065.82189</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>1224635.4291</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>1257941.60896</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>27290538.2703555</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>28899654.6865236</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>30607050.1499728</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>32478160.0391071</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>34677209.4583278</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>36797855.1862464</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>38953160.9736572</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>41336712.5276652</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>44143087.0870978</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>47903642.9233841</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>52426737.6630606</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>57618923.0172985</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>63852466.1292683</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>69625755.9629028</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>75835204.2729793</t>
         </is>
       </c>
     </row>
@@ -3374,7 +4940,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3397,36 +4963,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3438,331 +5019,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3799,6 +5744,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Ochoa 1</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpO1</t>
